--- a/data/output/sim_gridrnd/REL2/group_480_60/results/REL2_G3_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_480_60/results/REL2_G3_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>481</v>
       </c>
       <c r="C2" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D2" t="n">
         <v>59</v>
-      </c>
-      <c r="D2" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E2" t="n">
         <v>481</v>
@@ -852,228 +907,261 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>499.1704993870755</v>
-      </c>
-      <c r="J2" t="n">
-        <v>76.45980495628562</v>
-      </c>
-      <c r="K2" t="n">
-        <v>477.2775918189054</v>
-      </c>
-      <c r="L2" t="n">
-        <v>79.86013510511752</v>
-      </c>
-      <c r="M2" t="n">
-        <v>459.7601465731295</v>
-      </c>
-      <c r="N2" t="n">
-        <v>96.89191646148583</v>
-      </c>
-      <c r="O2" t="n">
-        <v>451.3744140835284</v>
-      </c>
-      <c r="P2" t="n">
-        <v>87.14120818599746</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>458.4720651292599</v>
-      </c>
       <c r="R2" t="n">
-        <v>85.77458263661487</v>
+        <v>499.17</v>
       </c>
       <c r="S2" t="n">
-        <v>460.4443362165511</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>82.0274790749765</v>
+        <v>477.28</v>
       </c>
       <c r="U2" t="n">
-        <v>460.839285267672</v>
+        <v>79.86</v>
       </c>
       <c r="V2" t="n">
-        <v>80.31975314495082</v>
+        <v>459.76</v>
       </c>
       <c r="W2" t="n">
-        <v>463.0222523003091</v>
+        <v>96.89</v>
       </c>
       <c r="X2" t="n">
-        <v>80.32717365457698</v>
+        <v>451.37</v>
       </c>
       <c r="Y2" t="n">
-        <v>465.5425256437089</v>
+        <v>87.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.66714974211311</v>
+        <v>458.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>85.77</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>460.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>82.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>460.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>463.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>80.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>465.54</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>81.67</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>499.9</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>497.8</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>491.2375</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>484.08</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>478.7666666666667</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>478.2857142857143</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>476.70625</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>477.4611111111111</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>474.825</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>99.43485304459398</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>93.83474836114819</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>96.62857286408612</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>97.60570475131051</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>96.49229099893019</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>97.91448789007431</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>96.20087037515566</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>96.30589943213292</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>95.03406954876762</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>324</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>324</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>322</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>322</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>322</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>322</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>322</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>322</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>322</v>
       </c>
-      <c r="BK2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>669</v>
-      </c>
       <c r="BT2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.4</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>1</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.875</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.7586206896551724</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>465.54</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>81.67</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>479</v>
       </c>
       <c r="C3" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D3" t="n">
         <v>59</v>
-      </c>
-      <c r="D3" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E3" t="n">
         <v>479</v>
@@ -1098,736 +1186,835 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>456.9871115268629</v>
-      </c>
-      <c r="J3" t="n">
-        <v>43.67664230063325</v>
-      </c>
-      <c r="K3" t="n">
-        <v>466.0644615369999</v>
-      </c>
-      <c r="L3" t="n">
-        <v>41.60806734133092</v>
-      </c>
-      <c r="M3" t="n">
-        <v>468.3083117265584</v>
-      </c>
-      <c r="N3" t="n">
-        <v>53.727892292769</v>
-      </c>
-      <c r="O3" t="n">
-        <v>466.8261625585396</v>
-      </c>
-      <c r="P3" t="n">
-        <v>51.44423373740632</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>466.773939448478</v>
-      </c>
       <c r="R3" t="n">
-        <v>57.36505470462249</v>
+        <v>456.99</v>
       </c>
       <c r="S3" t="n">
-        <v>467.1071323421602</v>
+        <v>43.68</v>
       </c>
       <c r="T3" t="n">
-        <v>58.71846039359954</v>
+        <v>466.06</v>
       </c>
       <c r="U3" t="n">
-        <v>475.0345801218091</v>
+        <v>41.61</v>
       </c>
       <c r="V3" t="n">
-        <v>65.94934044156803</v>
+        <v>468.31</v>
       </c>
       <c r="W3" t="n">
-        <v>482.0525061391659</v>
+        <v>53.73</v>
       </c>
       <c r="X3" t="n">
-        <v>71.92019097293691</v>
+        <v>466.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>479.4051526902459</v>
+        <v>51.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>68.74797140310173</v>
+        <v>466.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>57.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>467.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>58.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>475.03</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>65.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>482.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>71.92</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>479.41</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>475.775</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>472.6666666666667</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>472.925</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>473.09</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>471.8333333333333</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>471.3785714285714</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>475.60625</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>479.7944444444444</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>484.36</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>84.47617637535448</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>75.7455535915402</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>70.82403811560027</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>68.48957511913767</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>68.35499656612936</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>69.04630618620509</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>70.49318201739442</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>74.08611335033055</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>76.96064188921504</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>334</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>334</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>334</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>334</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>334</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>334</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>334</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>334</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>334</v>
       </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.5365853658536586</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.6904761904761905</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.6904761904761905</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.6904761904761905</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.6904761904761905</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>479.41</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>68.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S04_G3_481_59_REL2</t>
+          <t>S03_G3_482_60_REL2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D4" t="n">
-        <v>87.47220163083766</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>481.1788385571767</v>
-      </c>
-      <c r="J4" t="n">
-        <v>81.53016959321322</v>
-      </c>
-      <c r="K4" t="n">
-        <v>480.0264095086691</v>
-      </c>
-      <c r="L4" t="n">
-        <v>72.06677043645097</v>
-      </c>
-      <c r="M4" t="n">
-        <v>482.977845564452</v>
-      </c>
-      <c r="N4" t="n">
-        <v>65.16457169656321</v>
-      </c>
-      <c r="O4" t="n">
-        <v>486.218837761537</v>
-      </c>
-      <c r="P4" t="n">
-        <v>59.61366107511633</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>488.3483410631188</v>
-      </c>
       <c r="R4" t="n">
-        <v>60.20349750630487</v>
+        <v>483.41</v>
       </c>
       <c r="S4" t="n">
-        <v>484.9846243369743</v>
+        <v>49.74</v>
       </c>
       <c r="T4" t="n">
-        <v>64.50123687034738</v>
+        <v>482.74</v>
       </c>
       <c r="U4" t="n">
-        <v>486.1876508615352</v>
+        <v>43.06</v>
       </c>
       <c r="V4" t="n">
-        <v>65.48926674241378</v>
+        <v>486.56</v>
       </c>
       <c r="W4" t="n">
-        <v>485.7928414141333</v>
+        <v>45.15</v>
       </c>
       <c r="X4" t="n">
-        <v>63.98894751451432</v>
+        <v>488.98</v>
       </c>
       <c r="Y4" t="n">
-        <v>480.2589750509101</v>
+        <v>48.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>64.24966796043212</v>
+        <v>484.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>51.13</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>478.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>60.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>477.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>478.48</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>68.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>480.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>70.22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>480.725</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>479.6333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>481.9875</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>484.35</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>486.05</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>485.5642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>484.9875</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>486.4388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>484.01</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>109.4189168973994</v>
+        <v>490.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>104.8449596096806</v>
+        <v>487.2666666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>98.43392374456076</v>
+        <v>486.7375</v>
       </c>
       <c r="AV4" t="n">
-        <v>92.25089430460824</v>
+        <v>486.67</v>
       </c>
       <c r="AW4" t="n">
-        <v>86.4011815119832</v>
+        <v>487.0083333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>83.37661634451966</v>
+        <v>485.7642857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>81.47507191620024</v>
+        <v>481.33125</v>
       </c>
       <c r="AZ4" t="n">
-        <v>79.65712382796161</v>
+        <v>478.2166666666666</v>
       </c>
       <c r="BA4" t="n">
-        <v>79.62738159703608</v>
+        <v>475.76</v>
       </c>
       <c r="BB4" t="n">
-        <v>306</v>
+        <v>75.21728524747486</v>
       </c>
       <c r="BC4" t="n">
-        <v>306</v>
+        <v>69.89178937630815</v>
       </c>
       <c r="BD4" t="n">
-        <v>306</v>
+        <v>65.19178317663969</v>
       </c>
       <c r="BE4" t="n">
-        <v>306</v>
+        <v>63.56430680814509</v>
       </c>
       <c r="BF4" t="n">
-        <v>306</v>
+        <v>61.6174347396002</v>
       </c>
       <c r="BG4" t="n">
-        <v>306</v>
+        <v>61.73533495197587</v>
       </c>
       <c r="BH4" t="n">
-        <v>306</v>
+        <v>66.8246513154951</v>
       </c>
       <c r="BI4" t="n">
-        <v>306</v>
+        <v>69.72973819604437</v>
       </c>
       <c r="BJ4" t="n">
-        <v>306</v>
+        <v>71.87602103622598</v>
       </c>
       <c r="BK4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BL4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BM4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BN4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BO4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BP4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BQ4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BR4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BS4" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BT4" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CE4" t="n">
         <v>0.5</v>
       </c>
-      <c r="BX4" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>1</v>
+      <c r="CF4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>480.97</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>70.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S03_G3_482_60_REL2</t>
+          <t>S04_G3_481_59_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D5" t="n">
-        <v>88.95478131949592</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>483.4136801035856</v>
-      </c>
-      <c r="J5" t="n">
-        <v>49.74131880327869</v>
-      </c>
-      <c r="K5" t="n">
-        <v>482.7416319128413</v>
-      </c>
-      <c r="L5" t="n">
-        <v>43.06248123523088</v>
-      </c>
-      <c r="M5" t="n">
-        <v>486.5643890145325</v>
-      </c>
-      <c r="N5" t="n">
-        <v>45.14668225589737</v>
-      </c>
-      <c r="O5" t="n">
-        <v>488.9837014167501</v>
-      </c>
-      <c r="P5" t="n">
-        <v>48.54501425371181</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>484.895576275446</v>
-      </c>
       <c r="R5" t="n">
-        <v>51.12835192287699</v>
+        <v>481.18</v>
       </c>
       <c r="S5" t="n">
-        <v>478.3754196795282</v>
+        <v>81.53</v>
       </c>
       <c r="T5" t="n">
-        <v>60.73574097791964</v>
+        <v>480.03</v>
       </c>
       <c r="U5" t="n">
-        <v>477.3215597195108</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>67.49008776334769</v>
+        <v>482.98</v>
       </c>
       <c r="W5" t="n">
-        <v>478.4818215255499</v>
+        <v>65.16</v>
       </c>
       <c r="X5" t="n">
-        <v>68.45130741366791</v>
+        <v>486.22</v>
       </c>
       <c r="Y5" t="n">
-        <v>480.9684482997448</v>
+        <v>59.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>70.22393329728376</v>
+        <v>488.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>60.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>484.98</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>486.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>485.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>63.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>480.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>64.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>490.6</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>487.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>486.7375</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>486.67</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>487.0083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>485.7642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>481.33125</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>478.2166666666666</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>475.76</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>75.21728524747486</v>
+        <v>480.725</v>
       </c>
       <c r="AT5" t="n">
-        <v>69.89178937630815</v>
+        <v>479.6333333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>65.19178317663969</v>
+        <v>481.9875</v>
       </c>
       <c r="AV5" t="n">
-        <v>63.56430680814509</v>
+        <v>484.35</v>
       </c>
       <c r="AW5" t="n">
-        <v>61.6174347396002</v>
+        <v>486.05</v>
       </c>
       <c r="AX5" t="n">
-        <v>61.73533495197587</v>
+        <v>485.5642857142857</v>
       </c>
       <c r="AY5" t="n">
-        <v>66.8246513154951</v>
+        <v>484.9875</v>
       </c>
       <c r="AZ5" t="n">
-        <v>69.72973819604437</v>
+        <v>486.4388888888889</v>
       </c>
       <c r="BA5" t="n">
-        <v>71.87602103622598</v>
+        <v>484.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>322</v>
+        <v>109.4189168973994</v>
       </c>
       <c r="BC5" t="n">
-        <v>322</v>
+        <v>104.8449596096806</v>
       </c>
       <c r="BD5" t="n">
-        <v>322</v>
+        <v>98.43392374456076</v>
       </c>
       <c r="BE5" t="n">
-        <v>322</v>
+        <v>92.25089430460824</v>
       </c>
       <c r="BF5" t="n">
-        <v>322</v>
+        <v>86.4011815119832</v>
       </c>
       <c r="BG5" t="n">
-        <v>322</v>
+        <v>83.37661634451966</v>
       </c>
       <c r="BH5" t="n">
-        <v>322</v>
+        <v>81.47507191620024</v>
       </c>
       <c r="BI5" t="n">
-        <v>322</v>
+        <v>79.65712382796161</v>
       </c>
       <c r="BJ5" t="n">
-        <v>322</v>
+        <v>79.62738159703608</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
         <v>0.5</v>
       </c>
-      <c r="BW5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.3</v>
+      <c r="CG5" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>480.26</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>64.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S07_G3_480_61_REL2</t>
+          <t>S05_G3_480_59_REL2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D6" t="n">
-        <v>90.43736100815418</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
         <v>480</v>
@@ -1836,720 +2023,819 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>475.0506573783846</v>
-      </c>
-      <c r="J6" t="n">
-        <v>63.75242065957743</v>
-      </c>
-      <c r="K6" t="n">
-        <v>495.4433941775437</v>
-      </c>
-      <c r="L6" t="n">
-        <v>68.75958796190348</v>
-      </c>
-      <c r="M6" t="n">
-        <v>489.4961428498109</v>
-      </c>
-      <c r="N6" t="n">
-        <v>64.15631377222674</v>
-      </c>
-      <c r="O6" t="n">
-        <v>482.1890087551255</v>
-      </c>
-      <c r="P6" t="n">
-        <v>70.12114861530752</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>478.6733762291477</v>
-      </c>
       <c r="R6" t="n">
-        <v>73.54152072619871</v>
+        <v>463.51</v>
       </c>
       <c r="S6" t="n">
-        <v>471.7921965008064</v>
+        <v>38.18</v>
       </c>
       <c r="T6" t="n">
-        <v>75.80825280770556</v>
+        <v>476.03</v>
       </c>
       <c r="U6" t="n">
-        <v>474.7773886160296</v>
+        <v>41.51</v>
       </c>
       <c r="V6" t="n">
-        <v>71.24886213157322</v>
+        <v>472.22</v>
       </c>
       <c r="W6" t="n">
-        <v>479.9722346119788</v>
+        <v>38.09</v>
       </c>
       <c r="X6" t="n">
-        <v>75.00971657105518</v>
+        <v>472.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>484.451940978929</v>
+        <v>41.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>75.48509430335935</v>
+        <v>485.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>483.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>54.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>483.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>481.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>60.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>482.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>56.14</v>
       </c>
       <c r="AJ6" t="n">
-        <v>477.15</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>479.4</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>481.8625</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>482.62</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>481.7416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>479.0857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>476.5375</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>477.45</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>476.945</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>88.17328110034242</v>
+        <v>485.625</v>
       </c>
       <c r="AT6" t="n">
-        <v>83.32630637039742</v>
+        <v>483.1333333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>80.45010002324423</v>
+        <v>480.7125</v>
       </c>
       <c r="AV6" t="n">
-        <v>78.68364251863279</v>
+        <v>479.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>78.57740301059134</v>
+        <v>480.475</v>
       </c>
       <c r="AX6" t="n">
-        <v>80.52342034768391</v>
+        <v>484.8571428571428</v>
       </c>
       <c r="AY6" t="n">
-        <v>81.51739749127177</v>
+        <v>486.66875</v>
       </c>
       <c r="AZ6" t="n">
-        <v>79.37857778463351</v>
+        <v>488.4777777777778</v>
       </c>
       <c r="BA6" t="n">
-        <v>79.45440186043817</v>
+        <v>490.12</v>
       </c>
       <c r="BB6" t="n">
-        <v>322</v>
+        <v>83.98264329610018</v>
       </c>
       <c r="BC6" t="n">
-        <v>322</v>
+        <v>72.29717990504348</v>
       </c>
       <c r="BD6" t="n">
-        <v>322</v>
+        <v>66.35193926141119</v>
       </c>
       <c r="BE6" t="n">
-        <v>322</v>
+        <v>62.74680151210897</v>
       </c>
       <c r="BF6" t="n">
-        <v>322</v>
+        <v>59.98221437781925</v>
       </c>
       <c r="BG6" t="n">
-        <v>322</v>
+        <v>62.50286524044562</v>
       </c>
       <c r="BH6" t="n">
-        <v>322</v>
+        <v>65.35027944421891</v>
       </c>
       <c r="BI6" t="n">
-        <v>322</v>
+        <v>67.54278113870214</v>
       </c>
       <c r="BJ6" t="n">
-        <v>322</v>
+        <v>68.7314018480636</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>327</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD6" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BX6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.5769230769230769</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.4838709677419355</v>
+      <c r="CE6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>482.21</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>56.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G3_480_59_REL2</t>
+          <t>S06_G3_479_59_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D7" t="n">
         <v>59</v>
       </c>
-      <c r="D7" t="n">
-        <v>87.47220163083766</v>
-      </c>
       <c r="E7" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>463.5105757611307</v>
-      </c>
-      <c r="J7" t="n">
-        <v>38.18082586871896</v>
-      </c>
-      <c r="K7" t="n">
-        <v>476.0258395964332</v>
-      </c>
-      <c r="L7" t="n">
-        <v>41.51073590073753</v>
-      </c>
-      <c r="M7" t="n">
-        <v>472.2216147854677</v>
-      </c>
-      <c r="N7" t="n">
-        <v>38.09323262209626</v>
-      </c>
-      <c r="O7" t="n">
-        <v>472.8997872001522</v>
-      </c>
-      <c r="P7" t="n">
-        <v>41.70022464775226</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>485.1049664204422</v>
-      </c>
       <c r="R7" t="n">
-        <v>48.59666365507966</v>
+        <v>478.15</v>
       </c>
       <c r="S7" t="n">
-        <v>483.2652075030046</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>54.42264256029987</v>
+        <v>463.31</v>
       </c>
       <c r="U7" t="n">
-        <v>483.2382652395723</v>
+        <v>91.86</v>
       </c>
       <c r="V7" t="n">
-        <v>58.79784068170751</v>
+        <v>467.06</v>
       </c>
       <c r="W7" t="n">
-        <v>481.8180263439037</v>
+        <v>80.62</v>
       </c>
       <c r="X7" t="n">
-        <v>60.05038254344076</v>
+        <v>468.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>482.2076930533452</v>
+        <v>73.92</v>
       </c>
       <c r="Z7" t="n">
-        <v>56.1355856735162</v>
+        <v>471.32</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>71.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>68.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>481.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>63.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>483.41</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>61.99</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>482.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>485.625</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>483.1333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>480.7125</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>479.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>480.475</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>484.8571428571428</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>486.66875</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>488.4777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>490.12</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>83.98264329610018</v>
+        <v>498.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>72.29717990504348</v>
+        <v>491.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>66.35193926141119</v>
+        <v>487.5875</v>
       </c>
       <c r="AV7" t="n">
-        <v>62.74680151210897</v>
+        <v>484.34</v>
       </c>
       <c r="AW7" t="n">
-        <v>59.98221437781925</v>
+        <v>481.5833333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>62.50286524044562</v>
+        <v>479.7142857142857</v>
       </c>
       <c r="AY7" t="n">
-        <v>65.35027944421891</v>
+        <v>480.96875</v>
       </c>
       <c r="AZ7" t="n">
-        <v>67.54278113870214</v>
+        <v>482.5055555555555</v>
       </c>
       <c r="BA7" t="n">
-        <v>68.7314018480636</v>
+        <v>486.615</v>
       </c>
       <c r="BB7" t="n">
-        <v>327</v>
+        <v>102.5867925222345</v>
       </c>
       <c r="BC7" t="n">
-        <v>327</v>
+        <v>99.62655268551653</v>
       </c>
       <c r="BD7" t="n">
-        <v>327</v>
+        <v>97.84039218926915</v>
       </c>
       <c r="BE7" t="n">
-        <v>327</v>
+        <v>96.01637568665045</v>
       </c>
       <c r="BF7" t="n">
-        <v>327</v>
+        <v>93.29376393354964</v>
       </c>
       <c r="BG7" t="n">
-        <v>327</v>
+        <v>89.9025890072365</v>
       </c>
       <c r="BH7" t="n">
-        <v>327</v>
+        <v>85.72160039008547</v>
       </c>
       <c r="BI7" t="n">
-        <v>327</v>
+        <v>82.18816468069018</v>
       </c>
       <c r="BJ7" t="n">
-        <v>327</v>
+        <v>82.22205771567627</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>316</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.9375</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7916666666666666</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.6451612903225806</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7096774193548387</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7741935483870968</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.96875</v>
+        <v>669</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.8378378378378378</v>
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>482.2</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S06_G3_479_59_REL2</t>
+          <t>S07_G3_480_61_REL2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D8" t="n">
-        <v>87.47220163083766</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>478.1530377183655</v>
-      </c>
-      <c r="J8" t="n">
-        <v>77.71361212012819</v>
-      </c>
-      <c r="K8" t="n">
-        <v>463.3052420056511</v>
-      </c>
-      <c r="L8" t="n">
-        <v>91.85746279458424</v>
-      </c>
-      <c r="M8" t="n">
-        <v>467.0578109359435</v>
-      </c>
-      <c r="N8" t="n">
-        <v>80.62174999725035</v>
-      </c>
-      <c r="O8" t="n">
-        <v>468.0620202886441</v>
-      </c>
-      <c r="P8" t="n">
-        <v>73.91655322808192</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>471.3225719094343</v>
-      </c>
       <c r="R8" t="n">
-        <v>71.55339105628228</v>
+        <v>475.05</v>
       </c>
       <c r="S8" t="n">
-        <v>478.9969134008725</v>
+        <v>63.75</v>
       </c>
       <c r="T8" t="n">
-        <v>68.02407802601554</v>
+        <v>495.44</v>
       </c>
       <c r="U8" t="n">
-        <v>481.0923765410849</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>63.30807283900699</v>
+        <v>489.5</v>
       </c>
       <c r="W8" t="n">
-        <v>483.4075382648065</v>
+        <v>64.16</v>
       </c>
       <c r="X8" t="n">
-        <v>61.9890073254526</v>
+        <v>482.19</v>
       </c>
       <c r="Y8" t="n">
-        <v>482.1991699233469</v>
+        <v>70.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>72.23917212970647</v>
+        <v>478.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>471.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>75.81</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>474.78</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>71.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>479.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>484.45</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>498.5</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>491.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>487.5875</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>484.34</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>481.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>479.7142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>480.96875</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>482.5055555555555</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>486.615</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>102.5867925222345</v>
+        <v>477.15</v>
       </c>
       <c r="AT8" t="n">
-        <v>99.62655268551653</v>
+        <v>479.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>97.84039218926915</v>
+        <v>481.8625</v>
       </c>
       <c r="AV8" t="n">
-        <v>96.01637568665045</v>
+        <v>482.62</v>
       </c>
       <c r="AW8" t="n">
-        <v>93.29376393354964</v>
+        <v>481.7416666666667</v>
       </c>
       <c r="AX8" t="n">
-        <v>89.9025890072365</v>
+        <v>479.0857142857143</v>
       </c>
       <c r="AY8" t="n">
-        <v>85.72160039008547</v>
+        <v>476.5375</v>
       </c>
       <c r="AZ8" t="n">
-        <v>82.18816468069018</v>
+        <v>477.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>82.22205771567627</v>
+        <v>476.945</v>
       </c>
       <c r="BB8" t="n">
-        <v>316</v>
+        <v>88.17328110034242</v>
       </c>
       <c r="BC8" t="n">
-        <v>316</v>
+        <v>83.32630637039742</v>
       </c>
       <c r="BD8" t="n">
-        <v>316</v>
+        <v>80.45010002324423</v>
       </c>
       <c r="BE8" t="n">
-        <v>316</v>
+        <v>78.68364251863279</v>
       </c>
       <c r="BF8" t="n">
-        <v>316</v>
+        <v>78.57740301059134</v>
       </c>
       <c r="BG8" t="n">
-        <v>316</v>
+        <v>80.52342034768391</v>
       </c>
       <c r="BH8" t="n">
-        <v>316</v>
+        <v>81.51739749127177</v>
       </c>
       <c r="BI8" t="n">
-        <v>316</v>
+        <v>79.37857778463351</v>
       </c>
       <c r="BJ8" t="n">
-        <v>316</v>
+        <v>79.45440186043817</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>322</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.5625</v>
+        <v>669</v>
       </c>
       <c r="BV8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CI8" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="BW8" t="n">
-        <v>0.8461538461538461</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.7428571428571429</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.8285714285714286</v>
+      <c r="CJ8" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>484.45</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>479</v>
       </c>
       <c r="C9" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D9" t="n">
         <v>62</v>
-      </c>
-      <c r="D9" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E9" t="n">
         <v>479</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>503.6342496042512</v>
-      </c>
-      <c r="J9" t="n">
-        <v>68.65904548096276</v>
-      </c>
-      <c r="K9" t="n">
-        <v>490.3964411226106</v>
-      </c>
-      <c r="L9" t="n">
-        <v>66.95090896538198</v>
-      </c>
-      <c r="M9" t="n">
-        <v>501.2095826043392</v>
-      </c>
-      <c r="N9" t="n">
-        <v>74.64810872039206</v>
-      </c>
-      <c r="O9" t="n">
-        <v>508.7317780370427</v>
-      </c>
-      <c r="P9" t="n">
-        <v>74.32889980987389</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>503.8931447555646</v>
-      </c>
       <c r="R9" t="n">
-        <v>80.8432138689809</v>
+        <v>503.63</v>
       </c>
       <c r="S9" t="n">
-        <v>497.9351180236332</v>
+        <v>68.66</v>
       </c>
       <c r="T9" t="n">
-        <v>83.62708769912328</v>
+        <v>490.4</v>
       </c>
       <c r="U9" t="n">
-        <v>490.6528956254033</v>
+        <v>66.95</v>
       </c>
       <c r="V9" t="n">
-        <v>91.04678634514013</v>
+        <v>501.21</v>
       </c>
       <c r="W9" t="n">
-        <v>485.7829804305716</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>86.3748474748876</v>
+        <v>508.73</v>
       </c>
       <c r="Y9" t="n">
-        <v>485.7703354012872</v>
+        <v>74.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>83.95046244857524</v>
+        <v>503.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>80.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>497.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>83.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>490.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>91.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>485.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>86.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>485.77</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>83.95</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>502.5</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>501.4333333333333</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>500.8</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>501.43</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>503.7333333333333</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>505.9214285714286</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>505.025</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>504.5666666666667</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>502.54</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>90.14460605050088</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>84.66214554857967</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>81.23475241545333</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>80.75707461269261</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>81.45016199424583</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>83.36880778951381</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>82.25972206979549</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>82.13803422694426</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>80.78055706666053</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>328</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>328</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>328</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>328</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>328</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>328</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>328</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>328</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>328</v>
       </c>
-      <c r="BK9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>669</v>
-      </c>
       <c r="BT9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.65</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.7878787878787878</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.9428571428571428</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.6875</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>485.77</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>83.95</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>478</v>
       </c>
       <c r="C10" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D10" t="n">
         <v>60</v>
-      </c>
-      <c r="D10" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E10" t="n">
         <v>478</v>
@@ -2820,474 +3139,540 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>478.5823551207926</v>
-      </c>
-      <c r="J10" t="n">
-        <v>43.19031563305602</v>
-      </c>
-      <c r="K10" t="n">
-        <v>481.5446324545121</v>
-      </c>
-      <c r="L10" t="n">
-        <v>52.53816695436051</v>
-      </c>
-      <c r="M10" t="n">
-        <v>484.5031440721227</v>
-      </c>
-      <c r="N10" t="n">
-        <v>65.78255582071925</v>
-      </c>
-      <c r="O10" t="n">
-        <v>484.8054329288059</v>
-      </c>
-      <c r="P10" t="n">
-        <v>67.30693692861138</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>488.4697665817442</v>
-      </c>
       <c r="R10" t="n">
-        <v>66.43653906031147</v>
+        <v>478.58</v>
       </c>
       <c r="S10" t="n">
-        <v>483.748673522645</v>
+        <v>43.19</v>
       </c>
       <c r="T10" t="n">
-        <v>68.18702457499049</v>
+        <v>481.54</v>
       </c>
       <c r="U10" t="n">
-        <v>478.8555700832262</v>
+        <v>52.54</v>
       </c>
       <c r="V10" t="n">
-        <v>64.07950679384618</v>
+        <v>484.5</v>
       </c>
       <c r="W10" t="n">
-        <v>474.7318537940027</v>
+        <v>65.78</v>
       </c>
       <c r="X10" t="n">
-        <v>66.33551676748566</v>
+        <v>484.81</v>
       </c>
       <c r="Y10" t="n">
-        <v>477.0925948262428</v>
+        <v>67.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>76.37086138355308</v>
+        <v>488.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>66.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>483.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>68.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>478.86</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>64.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>474.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>66.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>477.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>76.37</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>487.325</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>487.0166666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>485.075</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>485.32</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>486.6166666666667</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>486.4</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>485.23125</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>484.2166666666666</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>482.54</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>76.68943457217559</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>69.64995612984181</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>68.81892454114637</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>71.2079883159186</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>73.31361666763473</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>76.92081271392956</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>76.59987123642898</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>76.33335334788674</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>78.80976081679223</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>330</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>330</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>330</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>330</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>330</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>330</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>330</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>330</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>330</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.6206896551724138</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>477.09</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>76.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S12_G3_481_62_REL2</t>
+          <t>S10_G3_478_58_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D11" t="n">
-        <v>91.91994069681246</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>499.7675745238097</v>
-      </c>
-      <c r="J11" t="n">
-        <v>37.54900499864011</v>
-      </c>
-      <c r="K11" t="n">
-        <v>490.4395909330577</v>
-      </c>
-      <c r="L11" t="n">
-        <v>37.17961628189646</v>
-      </c>
-      <c r="M11" t="n">
-        <v>485.3130050573498</v>
-      </c>
-      <c r="N11" t="n">
-        <v>37.55160316837962</v>
-      </c>
-      <c r="O11" t="n">
-        <v>486.3233572714495</v>
-      </c>
-      <c r="P11" t="n">
-        <v>51.73054524303605</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>483.5883987127238</v>
-      </c>
       <c r="R11" t="n">
-        <v>63.84562362799489</v>
+        <v>448.37</v>
       </c>
       <c r="S11" t="n">
-        <v>487.8655405121254</v>
+        <v>61.95</v>
       </c>
       <c r="T11" t="n">
-        <v>68.8935931710925</v>
+        <v>451.02</v>
       </c>
       <c r="U11" t="n">
-        <v>490.2384099904278</v>
+        <v>69.13</v>
       </c>
       <c r="V11" t="n">
-        <v>70.44463024961121</v>
+        <v>456.86</v>
       </c>
       <c r="W11" t="n">
-        <v>489.2422487206078</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>65.66100078395468</v>
+        <v>458.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>485.5914546734498</v>
+        <v>77.58</v>
       </c>
       <c r="Z11" t="n">
-        <v>68.76376666988089</v>
+        <v>469.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>80.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>485.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>85.39</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>477.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>83.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>476.96</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>476.76</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>494.775</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>494.55</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>493.55</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>493.32</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>489.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>489.3285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>489.95</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>491.0333333333334</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>492.175</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>71.45680076101924</v>
+        <v>478.825</v>
       </c>
       <c r="AT11" t="n">
-        <v>63.38018223388128</v>
+        <v>470.6666666666667</v>
       </c>
       <c r="AU11" t="n">
-        <v>58.77476073962361</v>
+        <v>466.6875</v>
       </c>
       <c r="AV11" t="n">
-        <v>56.40848872288638</v>
+        <v>466.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>60.78859313683412</v>
+        <v>465.7416666666667</v>
       </c>
       <c r="AX11" t="n">
-        <v>67.84219534616901</v>
+        <v>468.7285714285715</v>
       </c>
       <c r="AY11" t="n">
-        <v>73.18971922339914</v>
+        <v>474.7625</v>
       </c>
       <c r="AZ11" t="n">
-        <v>76.8374836189271</v>
+        <v>478.25</v>
       </c>
       <c r="BA11" t="n">
-        <v>78.31094671244882</v>
+        <v>481.125</v>
       </c>
       <c r="BB11" t="n">
-        <v>342</v>
+        <v>94.60361713486435</v>
       </c>
       <c r="BC11" t="n">
-        <v>342</v>
+        <v>94.77704832336195</v>
       </c>
       <c r="BD11" t="n">
-        <v>342</v>
+        <v>94.20623569461843</v>
       </c>
       <c r="BE11" t="n">
-        <v>342</v>
+        <v>91.97025334313264</v>
       </c>
       <c r="BF11" t="n">
-        <v>342</v>
+        <v>90.63953293434137</v>
       </c>
       <c r="BG11" t="n">
-        <v>342</v>
+        <v>89.55739124455677</v>
       </c>
       <c r="BH11" t="n">
-        <v>342</v>
+        <v>90.24712512734132</v>
       </c>
       <c r="BI11" t="n">
-        <v>342</v>
+        <v>89.36540935333363</v>
       </c>
       <c r="BJ11" t="n">
-        <v>342</v>
+        <v>87.72086054639455</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>319</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.8181818181818182</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.6842105263157895</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.5862068965517241</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.5128205128205128</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.5128205128205128</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.5128205128205128</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.5384615384615384</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.5384615384615384</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>476.76</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>482</v>
       </c>
       <c r="C12" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D12" t="n">
         <v>62</v>
-      </c>
-      <c r="D12" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E12" t="n">
         <v>482</v>
@@ -3312,720 +3697,819 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>465.7162441637712</v>
-      </c>
-      <c r="J12" t="n">
-        <v>104.9977304658525</v>
-      </c>
-      <c r="K12" t="n">
-        <v>483.8454615796189</v>
-      </c>
-      <c r="L12" t="n">
-        <v>99.17615597317135</v>
-      </c>
-      <c r="M12" t="n">
-        <v>477.0122738764176</v>
-      </c>
-      <c r="N12" t="n">
-        <v>81.58420460995396</v>
-      </c>
-      <c r="O12" t="n">
-        <v>480.4094199865743</v>
-      </c>
-      <c r="P12" t="n">
-        <v>77.97402082441852</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>481.0200362009718</v>
-      </c>
       <c r="R12" t="n">
-        <v>82.48252541438249</v>
+        <v>465.72</v>
       </c>
       <c r="S12" t="n">
-        <v>481.9987747498591</v>
+        <v>105</v>
       </c>
       <c r="T12" t="n">
-        <v>80.41178615127981</v>
+        <v>483.85</v>
       </c>
       <c r="U12" t="n">
-        <v>487.639464539775</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>78.83657202975323</v>
+        <v>477.01</v>
       </c>
       <c r="W12" t="n">
-        <v>485.5529957990893</v>
+        <v>81.58</v>
       </c>
       <c r="X12" t="n">
-        <v>79.18429365161079</v>
+        <v>480.41</v>
       </c>
       <c r="Y12" t="n">
-        <v>488.7209989273457</v>
+        <v>77.97</v>
       </c>
       <c r="Z12" t="n">
-        <v>80.08601700259644</v>
+        <v>481.02</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>82.48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>80.41</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>487.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>78.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>485.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>488.72</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>80.09</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>490.525</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>482.9333333333333</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>481.9875</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>483.47</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>483.5083333333333</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>483.8071428571429</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>484.09375</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>484.5277777777778</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>485.62</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>130.9896918654289</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>125.6835797637154</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>117.7176169642845</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>110.1511193769723</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>105.5257469240985</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>101.9319027886876</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>98.94353167811173</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>96.53038845390465</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>94.53192899756147</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>269</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>269</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>269</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>269</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>269</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>269</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>269</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>269</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>269</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>706</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>706</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>706</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>706</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>706</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>706</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>706</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>706</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>706</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>1</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.1875</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.4423076923076923</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.4838709677419355</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.4444444444444444</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>488.72</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>80.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G3_478_58_REL2</t>
+          <t>S12_G3_481_62_REL2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D13" t="n">
-        <v>85.9896219421794</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>448.365281201972</v>
-      </c>
-      <c r="J13" t="n">
-        <v>61.95245173026743</v>
-      </c>
-      <c r="K13" t="n">
-        <v>451.0248442831694</v>
-      </c>
-      <c r="L13" t="n">
-        <v>69.13494486855519</v>
-      </c>
-      <c r="M13" t="n">
-        <v>456.8646993759379</v>
-      </c>
-      <c r="N13" t="n">
-        <v>77.9253137020297</v>
-      </c>
-      <c r="O13" t="n">
-        <v>458.4586861560495</v>
-      </c>
-      <c r="P13" t="n">
-        <v>77.58422474361727</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>469.1018622306965</v>
-      </c>
       <c r="R13" t="n">
-        <v>80.80642184930737</v>
+        <v>499.77</v>
       </c>
       <c r="S13" t="n">
-        <v>485.6987683072825</v>
+        <v>37.55</v>
       </c>
       <c r="T13" t="n">
-        <v>85.38634344412212</v>
+        <v>490.44</v>
       </c>
       <c r="U13" t="n">
-        <v>477.6265579414514</v>
+        <v>37.18</v>
       </c>
       <c r="V13" t="n">
-        <v>83.42232162281452</v>
+        <v>485.31</v>
       </c>
       <c r="W13" t="n">
-        <v>476.9646709566304</v>
+        <v>37.55</v>
       </c>
       <c r="X13" t="n">
-        <v>77.35430105348425</v>
+        <v>486.32</v>
       </c>
       <c r="Y13" t="n">
-        <v>476.7576066432006</v>
+        <v>51.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.89541526541112</v>
+        <v>483.59</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>63.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>487.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>68.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>490.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>70.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>489.24</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>65.66</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>485.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>478.825</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>470.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>466.6875</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>466.15</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>465.7416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>468.7285714285715</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>474.7625</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>478.25</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>481.125</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>94.60361713486435</v>
+        <v>494.775</v>
       </c>
       <c r="AT13" t="n">
-        <v>94.77704832336195</v>
+        <v>494.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>94.20623569461843</v>
+        <v>493.55</v>
       </c>
       <c r="AV13" t="n">
-        <v>91.97025334313264</v>
+        <v>493.32</v>
       </c>
       <c r="AW13" t="n">
-        <v>90.63953293434137</v>
+        <v>489.2833333333334</v>
       </c>
       <c r="AX13" t="n">
-        <v>89.55739124455677</v>
+        <v>489.3285714285714</v>
       </c>
       <c r="AY13" t="n">
-        <v>90.24712512734132</v>
+        <v>489.95</v>
       </c>
       <c r="AZ13" t="n">
-        <v>89.36540935333363</v>
+        <v>491.0333333333334</v>
       </c>
       <c r="BA13" t="n">
-        <v>87.72086054639455</v>
+        <v>492.175</v>
       </c>
       <c r="BB13" t="n">
-        <v>319</v>
+        <v>71.45680076101924</v>
       </c>
       <c r="BC13" t="n">
-        <v>319</v>
+        <v>63.38018223388128</v>
       </c>
       <c r="BD13" t="n">
-        <v>319</v>
+        <v>58.77476073962361</v>
       </c>
       <c r="BE13" t="n">
-        <v>319</v>
+        <v>56.40848872288638</v>
       </c>
       <c r="BF13" t="n">
-        <v>319</v>
+        <v>60.78859313683412</v>
       </c>
       <c r="BG13" t="n">
-        <v>319</v>
+        <v>67.84219534616901</v>
       </c>
       <c r="BH13" t="n">
-        <v>319</v>
+        <v>73.18971922339914</v>
       </c>
       <c r="BI13" t="n">
-        <v>319</v>
+        <v>76.8374836189271</v>
       </c>
       <c r="BJ13" t="n">
-        <v>319</v>
+        <v>78.31094671244882</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7083333333333334</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.6129032258064516</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.5555555555555556</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.5128205128205128</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>485.59</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S15_G3_480_61_REL2</t>
+          <t>S13_G3_482_61_REL2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C14" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D14" t="n">
         <v>61</v>
       </c>
-      <c r="D14" t="n">
-        <v>90.43736100815418</v>
-      </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>478.8749138696346</v>
-      </c>
-      <c r="J14" t="n">
-        <v>60.20631716133965</v>
-      </c>
-      <c r="K14" t="n">
-        <v>478.0679725509607</v>
-      </c>
-      <c r="L14" t="n">
-        <v>65.19320524750576</v>
-      </c>
-      <c r="M14" t="n">
-        <v>471.3760999596834</v>
-      </c>
-      <c r="N14" t="n">
-        <v>52.29301270918995</v>
-      </c>
-      <c r="O14" t="n">
-        <v>475.6818928159669</v>
-      </c>
-      <c r="P14" t="n">
-        <v>59.47944899272353</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>480.2144348977844</v>
-      </c>
       <c r="R14" t="n">
-        <v>73.40996495137141</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>483.7737523255068</v>
+        <v>81.45</v>
       </c>
       <c r="T14" t="n">
-        <v>75.57882685193907</v>
+        <v>502.61</v>
       </c>
       <c r="U14" t="n">
-        <v>484.665433628043</v>
+        <v>72.89</v>
       </c>
       <c r="V14" t="n">
-        <v>73.12302715154571</v>
+        <v>493.01</v>
       </c>
       <c r="W14" t="n">
-        <v>478.5703549410414</v>
+        <v>72.02</v>
       </c>
       <c r="X14" t="n">
-        <v>73.34349015275998</v>
+        <v>493.89</v>
       </c>
       <c r="Y14" t="n">
-        <v>482.5070060622149</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>74.48599344276988</v>
+        <v>482.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>484.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>82.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>479.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>82.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>478.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>80.47</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>477.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>87.45</v>
       </c>
       <c r="AJ14" t="n">
-        <v>508.675</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>497.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>488.04</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>487.3416666666666</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>487.8142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>490.825</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>492.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>491.03</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>106.6077829006869</v>
+        <v>508.975</v>
       </c>
       <c r="AT14" t="n">
-        <v>93.69907357540356</v>
+        <v>507.8166666666667</v>
       </c>
       <c r="AU14" t="n">
-        <v>86.76857149913211</v>
+        <v>507.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>81.63588916646893</v>
+        <v>505.22</v>
       </c>
       <c r="AW14" t="n">
-        <v>82.36114535318755</v>
+        <v>502.1166666666667</v>
       </c>
       <c r="AX14" t="n">
-        <v>86.42962337022166</v>
+        <v>498.45</v>
       </c>
       <c r="AY14" t="n">
-        <v>88.10054979964654</v>
+        <v>493.5625</v>
       </c>
       <c r="AZ14" t="n">
-        <v>88.99478605201793</v>
+        <v>488.6777777777778</v>
       </c>
       <c r="BA14" t="n">
-        <v>89.8169198982018</v>
+        <v>486.465</v>
       </c>
       <c r="BB14" t="n">
-        <v>333</v>
+        <v>118.4840680218231</v>
       </c>
       <c r="BC14" t="n">
-        <v>333</v>
+        <v>110.717732946845</v>
       </c>
       <c r="BD14" t="n">
-        <v>333</v>
+        <v>102.8725060451042</v>
       </c>
       <c r="BE14" t="n">
-        <v>333</v>
+        <v>98.37912176879809</v>
       </c>
       <c r="BF14" t="n">
-        <v>333</v>
+        <v>95.93532398907551</v>
       </c>
       <c r="BG14" t="n">
-        <v>333</v>
+        <v>94.96159562084634</v>
       </c>
       <c r="BH14" t="n">
-        <v>333</v>
+        <v>96.53022114213766</v>
       </c>
       <c r="BI14" t="n">
-        <v>333</v>
+        <v>97.39459576357724</v>
       </c>
       <c r="BJ14" t="n">
-        <v>333</v>
+        <v>96.72248329628432</v>
       </c>
       <c r="BK14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BL14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BM14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BN14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BO14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BP14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BQ14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BR14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BS14" t="n">
-        <v>706</v>
+        <v>321</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.3333333333333333</v>
+        <v>675</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.8</v>
+        <v>675</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.88</v>
+        <v>675</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.9090909090909091</v>
+        <v>675</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.8108108108108109</v>
+        <v>675</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.8108108108108109</v>
+        <v>675</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.8108108108108109</v>
+        <v>675</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.75</v>
+        <v>675</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.75</v>
+        <v>675</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>477.22</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>87.45</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>482</v>
       </c>
       <c r="C15" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D15" t="n">
         <v>59</v>
-      </c>
-      <c r="D15" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E15" t="n">
         <v>482</v>
@@ -4050,474 +4534,540 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>504.6554965291664</v>
-      </c>
-      <c r="J15" t="n">
-        <v>59.36050223047121</v>
-      </c>
-      <c r="K15" t="n">
-        <v>503.9536083447906</v>
-      </c>
-      <c r="L15" t="n">
-        <v>85.14588296030114</v>
-      </c>
-      <c r="M15" t="n">
-        <v>503.1064789678771</v>
-      </c>
-      <c r="N15" t="n">
-        <v>84.92078556768476</v>
-      </c>
-      <c r="O15" t="n">
-        <v>497.4719010849973</v>
-      </c>
-      <c r="P15" t="n">
-        <v>73.5199098350232</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>493.9819911094022</v>
-      </c>
       <c r="R15" t="n">
-        <v>71.30061627007913</v>
+        <v>504.66</v>
       </c>
       <c r="S15" t="n">
-        <v>498.2530576952983</v>
+        <v>59.36</v>
       </c>
       <c r="T15" t="n">
-        <v>71.51283542073411</v>
+        <v>503.95</v>
       </c>
       <c r="U15" t="n">
-        <v>497.8509869897816</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>68.66494834357162</v>
+        <v>503.11</v>
       </c>
       <c r="W15" t="n">
-        <v>492.5537567740552</v>
+        <v>84.92</v>
       </c>
       <c r="X15" t="n">
-        <v>68.00095143685328</v>
+        <v>497.47</v>
       </c>
       <c r="Y15" t="n">
-        <v>489.8237592016644</v>
+        <v>73.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>67.54509351925012</v>
+        <v>493.98</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>71.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>498.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>497.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>68.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>492.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>489.82</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>513.85</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>509.7166666666666</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>507.3625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>504.73</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>503</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>500.9642857142857</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>500.21875</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>498.7111111111111</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>497.585</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>98.56534634444297</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>93.38416919133326</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>92.79240859978795</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>89.97731436312156</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>85.22274735460402</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>82.05446020037857</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>80.38187543493558</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>78.92721604173533</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>77.99604332913306</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>317</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>317</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>317</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>317</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>317</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>317</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>317</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>317</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>317</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.8260869565217391</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>489.82</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>67.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S13_G3_482_61_REL2</t>
+          <t>S15_G3_480_61_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C16" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D16" t="n">
         <v>61</v>
       </c>
-      <c r="D16" t="n">
-        <v>90.43736100815418</v>
-      </c>
       <c r="E16" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>524.6904132076776</v>
-      </c>
-      <c r="J16" t="n">
-        <v>81.45314396044652</v>
-      </c>
-      <c r="K16" t="n">
-        <v>502.611992182572</v>
-      </c>
-      <c r="L16" t="n">
-        <v>72.88714314629138</v>
-      </c>
-      <c r="M16" t="n">
-        <v>493.0105903180682</v>
-      </c>
-      <c r="N16" t="n">
-        <v>72.02073718716625</v>
-      </c>
-      <c r="O16" t="n">
-        <v>493.8901547197519</v>
-      </c>
-      <c r="P16" t="n">
-        <v>77.17818758342133</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>482.5245288676709</v>
-      </c>
       <c r="R16" t="n">
-        <v>79.4558107509794</v>
+        <v>478.87</v>
       </c>
       <c r="S16" t="n">
-        <v>484.4753265994634</v>
+        <v>60.21</v>
       </c>
       <c r="T16" t="n">
-        <v>82.24504387966381</v>
+        <v>478.07</v>
       </c>
       <c r="U16" t="n">
-        <v>479.1322556626849</v>
+        <v>65.19</v>
       </c>
       <c r="V16" t="n">
-        <v>82.08970662743724</v>
+        <v>471.38</v>
       </c>
       <c r="W16" t="n">
-        <v>478.3181269224227</v>
+        <v>52.29</v>
       </c>
       <c r="X16" t="n">
-        <v>80.47090662282235</v>
+        <v>475.68</v>
       </c>
       <c r="Y16" t="n">
-        <v>477.2242611818554</v>
+        <v>59.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>87.44715543882772</v>
+        <v>480.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>73.41</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>483.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>75.58</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>484.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>73.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>478.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>73.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>482.51</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>508.975</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>507.8166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>507.35</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>505.22</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>502.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>498.45</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>493.5625</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>488.6777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>486.465</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>118.4840680218231</v>
+        <v>508.675</v>
       </c>
       <c r="AT16" t="n">
-        <v>110.717732946845</v>
+        <v>497.6833333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>102.8725060451042</v>
+        <v>491.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>98.37912176879809</v>
+        <v>488.04</v>
       </c>
       <c r="AW16" t="n">
-        <v>95.93532398907551</v>
+        <v>487.3416666666666</v>
       </c>
       <c r="AX16" t="n">
-        <v>94.96159562084634</v>
+        <v>487.8142857142857</v>
       </c>
       <c r="AY16" t="n">
-        <v>96.53022114213766</v>
+        <v>490.825</v>
       </c>
       <c r="AZ16" t="n">
-        <v>97.39459576357724</v>
+        <v>492.1833333333333</v>
       </c>
       <c r="BA16" t="n">
-        <v>96.72248329628432</v>
+        <v>491.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>321</v>
+        <v>106.6077829006869</v>
       </c>
       <c r="BC16" t="n">
-        <v>321</v>
+        <v>93.69907357540356</v>
       </c>
       <c r="BD16" t="n">
-        <v>321</v>
+        <v>86.76857149913211</v>
       </c>
       <c r="BE16" t="n">
-        <v>321</v>
+        <v>81.63588916646893</v>
       </c>
       <c r="BF16" t="n">
-        <v>321</v>
+        <v>82.36114535318755</v>
       </c>
       <c r="BG16" t="n">
-        <v>321</v>
+        <v>86.42962337022166</v>
       </c>
       <c r="BH16" t="n">
-        <v>321</v>
+        <v>88.10054979964654</v>
       </c>
       <c r="BI16" t="n">
-        <v>321</v>
+        <v>88.99478605201793</v>
       </c>
       <c r="BJ16" t="n">
-        <v>321</v>
+        <v>89.8169198982018</v>
       </c>
       <c r="BK16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BL16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BM16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BN16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BO16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BP16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BQ16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BR16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BS16" t="n">
-        <v>675</v>
+        <v>333</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.6666666666666666</v>
+        <v>706</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.8181818181818182</v>
+        <v>706</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.9230769230769231</v>
+        <v>706</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.8333333333333334</v>
+        <v>706</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.95</v>
+        <v>706</v>
       </c>
       <c r="BY16" t="n">
-        <v>1</v>
+        <v>706</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.7857142857142857</v>
+        <v>706</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.7586206896551724</v>
+        <v>706</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.7333333333333333</v>
+        <v>706</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.8108108108108109</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.8108108108108109</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.8108108108108109</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>482.51</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>478</v>
       </c>
       <c r="C17" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D17" t="n">
         <v>62</v>
-      </c>
-      <c r="D17" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E17" t="n">
         <v>478</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>460.8556972988953</v>
-      </c>
-      <c r="J17" t="n">
-        <v>102.6436382571634</v>
-      </c>
-      <c r="K17" t="n">
-        <v>492.3876383799799</v>
-      </c>
-      <c r="L17" t="n">
-        <v>92.47667593257842</v>
-      </c>
-      <c r="M17" t="n">
-        <v>491.7441730285421</v>
-      </c>
-      <c r="N17" t="n">
-        <v>81.24093532675226</v>
-      </c>
-      <c r="O17" t="n">
-        <v>482.4133604159073</v>
-      </c>
-      <c r="P17" t="n">
-        <v>78.49916059881225</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>480.2398386589569</v>
-      </c>
       <c r="R17" t="n">
-        <v>78.14019335384394</v>
+        <v>460.86</v>
       </c>
       <c r="S17" t="n">
-        <v>481.0586322743641</v>
+        <v>102.64</v>
       </c>
       <c r="T17" t="n">
-        <v>84.71994388646972</v>
+        <v>492.39</v>
       </c>
       <c r="U17" t="n">
-        <v>478.6527560664786</v>
+        <v>92.48</v>
       </c>
       <c r="V17" t="n">
-        <v>84.27353258741688</v>
+        <v>491.74</v>
       </c>
       <c r="W17" t="n">
-        <v>479.0749492868065</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>78.85002537142569</v>
+        <v>482.41</v>
       </c>
       <c r="Y17" t="n">
-        <v>474.8058538914206</v>
+        <v>78.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>79.80471776844408</v>
+        <v>480.24</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>78.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>481.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>84.72</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>478.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>84.27</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>479.07</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>474.81</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>507.125</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>495.9833333333333</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>494.9</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>494.21</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>493.3083333333333</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>492.0142857142857</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>490.7625</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>489.8222222222222</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>488.37</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>139.3214246804848</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>127.7044102170669</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>118.3911525410577</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>111.1961595559847</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>105.4337703516077</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>101.4136498078387</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>98.35989321745933</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>95.80229384609139</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>92.98302587031678</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>326</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>326</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>326</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>326</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>326</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>326</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>326</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>326</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>326</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>705</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>705</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>705</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>705</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>705</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>705</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>705</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>705</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>705</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.4117647058823529</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>1</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.8636363636363636</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.76</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>474.81</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>79.8</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>478</v>
       </c>
       <c r="C18" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D18" t="n">
         <v>62</v>
-      </c>
-      <c r="D18" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E18" t="n">
         <v>478</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>500.1740687515908</v>
-      </c>
-      <c r="J18" t="n">
-        <v>71.20581877052958</v>
-      </c>
-      <c r="K18" t="n">
-        <v>485.8847270549655</v>
-      </c>
-      <c r="L18" t="n">
-        <v>73.99783161412793</v>
-      </c>
-      <c r="M18" t="n">
-        <v>476.1714893363908</v>
-      </c>
-      <c r="N18" t="n">
-        <v>83.38481728024072</v>
-      </c>
-      <c r="O18" t="n">
-        <v>470.5828036160241</v>
-      </c>
-      <c r="P18" t="n">
-        <v>88.25583370827992</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>471.4126224482423</v>
-      </c>
       <c r="R18" t="n">
-        <v>77.78094301221091</v>
+        <v>500.17</v>
       </c>
       <c r="S18" t="n">
-        <v>470.1494896327613</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>75.62263705876099</v>
+        <v>485.88</v>
       </c>
       <c r="U18" t="n">
-        <v>470.3340441576597</v>
+        <v>74</v>
       </c>
       <c r="V18" t="n">
-        <v>71.69557653573692</v>
+        <v>476.17</v>
       </c>
       <c r="W18" t="n">
-        <v>475.0278703756169</v>
+        <v>83.38</v>
       </c>
       <c r="X18" t="n">
-        <v>70.47181539672046</v>
+        <v>470.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>474.8811169988871</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>67.5179827735255</v>
+        <v>471.41</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>470.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>75.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>470.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>475.03</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>70.47</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>474.88</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>67.52</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>510.375</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>506.2</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>501.5</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>495.05</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>487.9333333333333</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>484.4285714285714</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>485.21875</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>486.1777777777778</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>486.81</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>97.71992823881934</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>95.21393455441978</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>93.18221396811732</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>94.01865506376913</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>94.98532635213832</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>92.28156779716109</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>91.23463376611701</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>89.42788252463271</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>88.68581566406209</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>343</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>343</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>343</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>340</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>328</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>328</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>328</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>328</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>328</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.92</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.7741935483870968</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>474.88</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>67.52</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>479</v>
       </c>
       <c r="C19" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D19" t="n">
         <v>59</v>
-      </c>
-      <c r="D19" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E19" t="n">
         <v>479</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>512.5390162326266</v>
-      </c>
-      <c r="J19" t="n">
-        <v>57.40542384943765</v>
-      </c>
-      <c r="K19" t="n">
-        <v>482.1121982672798</v>
-      </c>
-      <c r="L19" t="n">
-        <v>64.76014950545282</v>
-      </c>
-      <c r="M19" t="n">
-        <v>472.0408747510166</v>
-      </c>
-      <c r="N19" t="n">
-        <v>56.9222598751423</v>
-      </c>
-      <c r="O19" t="n">
-        <v>482.9003486728751</v>
-      </c>
-      <c r="P19" t="n">
-        <v>72.99262960871015</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>478.3304864437634</v>
-      </c>
       <c r="R19" t="n">
-        <v>66.37600904203718</v>
+        <v>512.54</v>
       </c>
       <c r="S19" t="n">
-        <v>477.0210219334368</v>
+        <v>57.41</v>
       </c>
       <c r="T19" t="n">
-        <v>69.84894465044253</v>
+        <v>482.11</v>
       </c>
       <c r="U19" t="n">
-        <v>470.4209185017142</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>70.67592211560766</v>
+        <v>472.04</v>
       </c>
       <c r="W19" t="n">
-        <v>470.9071696460695</v>
+        <v>56.92</v>
       </c>
       <c r="X19" t="n">
-        <v>68.78118034661431</v>
+        <v>482.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>472.5568014760186</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>73.45403998829345</v>
+        <v>478.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>66.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>477.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>470.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>470.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>68.78</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>472.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>73.45</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>499.925</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>500.4833333333333</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>498.075</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>496.73</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>494.975</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>494.2714285714285</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>491.95</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>490.15</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>488.69</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>102.7719289251691</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>92.48197872498667</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>85.02893257591795</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>80.57342676093651</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>78.01051878860098</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>79.67145418683469</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>79.22442805094903</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>78.66331030975553</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>80.86373661908038</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>318</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>318</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>318</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>318</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>318</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>318</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>318</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>318</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>318</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.07407407407407407</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.75</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.875</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>472.56</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>73.45</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>478</v>
       </c>
       <c r="C20" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D20" t="n">
         <v>62</v>
-      </c>
-      <c r="D20" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E20" t="n">
         <v>478</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>445.5102829181623</v>
-      </c>
-      <c r="J20" t="n">
-        <v>65.20601714603704</v>
-      </c>
-      <c r="K20" t="n">
-        <v>447.7939331206342</v>
-      </c>
-      <c r="L20" t="n">
-        <v>58.08213179928019</v>
-      </c>
-      <c r="M20" t="n">
-        <v>445.8454264535538</v>
-      </c>
-      <c r="N20" t="n">
-        <v>54.80725121170733</v>
-      </c>
-      <c r="O20" t="n">
-        <v>455.3010191660833</v>
-      </c>
-      <c r="P20" t="n">
-        <v>56.13919447587653</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>456.2855239495651</v>
-      </c>
       <c r="R20" t="n">
-        <v>56.28563180209222</v>
+        <v>445.51</v>
       </c>
       <c r="S20" t="n">
-        <v>461.6362729709803</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>57.20662448430082</v>
+        <v>447.79</v>
       </c>
       <c r="U20" t="n">
-        <v>462.2567589751073</v>
+        <v>58.08</v>
       </c>
       <c r="V20" t="n">
-        <v>60.52697693388151</v>
+        <v>445.85</v>
       </c>
       <c r="W20" t="n">
-        <v>458.9901053245821</v>
+        <v>54.81</v>
       </c>
       <c r="X20" t="n">
-        <v>60.147794918909</v>
+        <v>455.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>461.2201235068036</v>
+        <v>56.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>65.39106374928518</v>
+        <v>456.29</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>56.29</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>461.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>57.21</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>462.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>60.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>458.99</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>60.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>461.22</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>65.39</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>457.5</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>455.4833333333333</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>455.6</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>455.74</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>456.45</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>457.0714285714286</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>458.20625</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>458.8611111111111</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>459.55</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>103.1232272574903</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>94.52133650957097</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>88.10839914559791</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>83.77357817355063</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>80.52937869705275</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>78.41042595190504</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>76.71188767679688</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>75.80045176418358</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>75.01124915637654</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>302</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>302</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>302</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>302</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>302</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>302</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>302</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>302</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>302</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.7878787878787878</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8297872340425532</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8363636363636363</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>461.22</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>65.39</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>478</v>
       </c>
       <c r="C21" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D21" t="n">
         <v>61</v>
-      </c>
-      <c r="D21" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E21" t="n">
         <v>478</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>475.8561370915749</v>
-      </c>
-      <c r="J21" t="n">
-        <v>56.30469581629229</v>
-      </c>
-      <c r="K21" t="n">
-        <v>478.7348403140605</v>
-      </c>
-      <c r="L21" t="n">
-        <v>56.34609835163748</v>
-      </c>
-      <c r="M21" t="n">
-        <v>477.4406856643565</v>
-      </c>
-      <c r="N21" t="n">
-        <v>63.26998780767428</v>
-      </c>
-      <c r="O21" t="n">
-        <v>474.2765467995837</v>
-      </c>
-      <c r="P21" t="n">
-        <v>61.07805791065904</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>482.4030910645574</v>
-      </c>
       <c r="R21" t="n">
-        <v>58.01168549210705</v>
+        <v>475.86</v>
       </c>
       <c r="S21" t="n">
-        <v>474.4740453000891</v>
+        <v>56.3</v>
       </c>
       <c r="T21" t="n">
-        <v>63.54692851150887</v>
+        <v>478.73</v>
       </c>
       <c r="U21" t="n">
-        <v>483.2013302477174</v>
+        <v>56.35</v>
       </c>
       <c r="V21" t="n">
-        <v>69.492017173825</v>
+        <v>477.44</v>
       </c>
       <c r="W21" t="n">
-        <v>477.5032921645701</v>
+        <v>63.27</v>
       </c>
       <c r="X21" t="n">
-        <v>69.97896438158966</v>
+        <v>474.28</v>
       </c>
       <c r="Y21" t="n">
-        <v>480.2201256395771</v>
+        <v>61.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>69.66656540433684</v>
+        <v>482.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>58.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>474.47</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>63.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>483.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>477.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>69.98</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>480.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>69.67</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>467.05</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>472.0333333333334</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>472.675</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>473.75</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>473.65</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>474.1</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>474.73125</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>475.3388888888889</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>475.035</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>101.2706645579064</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>91.33490874553692</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>86.3456390039474</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>82.92483041887996</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>79.72825199806319</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>77.94378010555336</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>76.42534935109882</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>75.18689039755748</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>74.983556697452</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>324</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>324</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>324</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>324</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>324</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>324</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>324</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>324</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>324</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.6</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.55</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.6170212765957447</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.6071428571428571</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.5538461538461539</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.6111111111111112</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>480.22</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>69.67</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>479.75</v>
       </c>
       <c r="C22" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="D22" t="n">
         <v>60.35</v>
-      </c>
-      <c r="D22" t="n">
-        <v>89.47368421052632</v>
       </c>
       <c r="E22" t="n">
         <v>479.75</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5142499999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>78.375</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4135</v>
+      </c>
       <c r="I22" t="n">
-        <v>481.8343065473252</v>
+        <v>2.421</v>
       </c>
       <c r="J22" t="n">
-        <v>65.05944499011659</v>
+        <v>2.4745</v>
       </c>
       <c r="K22" t="n">
-        <v>480.4841225572627</v>
+        <v>2.538</v>
       </c>
       <c r="L22" t="n">
-        <v>66.62970761879481</v>
+        <v>2.5615</v>
       </c>
       <c r="M22" t="n">
-        <v>478.1012392457775</v>
+        <v>2.5825</v>
       </c>
       <c r="N22" t="n">
-        <v>66.50769660426606</v>
+        <v>2.6745</v>
       </c>
       <c r="O22" t="n">
-        <v>478.3900316867694</v>
+        <v>2.535</v>
       </c>
       <c r="P22" t="n">
-        <v>67.42745470032183</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>479.2528281198486</v>
-      </c>
+        <v>2.456500000000001</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>69.16691203518391</v>
+        <v>481.8345</v>
       </c>
       <c r="S22" t="n">
-        <v>479.6527151913671</v>
+        <v>65.0595</v>
       </c>
       <c r="T22" t="n">
-        <v>71.55127552476461</v>
+        <v>480.4835</v>
       </c>
       <c r="U22" t="n">
-        <v>479.5009244388341</v>
+        <v>66.6305</v>
       </c>
       <c r="V22" t="n">
-        <v>72.04873741273779</v>
+        <v>478.1010000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>478.8883797867957</v>
+        <v>66.50699999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>71.33459071773811</v>
+        <v>478.3894999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>479.1102972035099</v>
+        <v>67.42749999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>73.05638546821311</v>
+        <v>479.2515</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>69.16749999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>479.6534999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>71.55199999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>479.501</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>72.04900000000001</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>478.887</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>71.33400000000002</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>479.1104999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>73.0575</v>
       </c>
       <c r="AJ22" t="n">
-        <v>491.785</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>488.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>486.990625</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>491.7844999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>488.6695</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>486.991</v>
+      </c>
+      <c r="AV22" t="n">
         <v>485.8819999999999</v>
       </c>
-      <c r="AN22" t="n">
-        <v>484.7558333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>484.3975</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>484.3671875</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>484.6430555555556</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>484.5085</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>98.75192348971558</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>91.83887731820889</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>87.49814315543001</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>84.61656001718528</v>
-      </c>
       <c r="AW22" t="n">
-        <v>82.93216998400439</v>
+        <v>484.756</v>
       </c>
       <c r="AX22" t="n">
-        <v>82.88946434458686</v>
+        <v>484.397</v>
       </c>
       <c r="AY22" t="n">
-        <v>82.78959303620195</v>
+        <v>484.3669999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>82.51452470555213</v>
+        <v>484.6435</v>
       </c>
       <c r="BA22" t="n">
-        <v>82.55614300830938</v>
+        <v>484.508</v>
       </c>
       <c r="BB22" t="n">
+        <v>98.75150000000001</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>91.83799999999999</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>87.49749999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>84.61699999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>82.932</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>82.88849999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>82.78900000000002</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>82.51500000000001</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>82.55549999999999</v>
+      </c>
+      <c r="BK22" t="n">
         <v>321.15</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>321.15</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>321.05</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>320.9</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>320.3</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>320.3</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>320.3</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>320.3</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>320.3</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>674.8</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6299512987012987</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6585565936901076</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6538365474510597</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7025715931665588</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.6561933733589268</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7389947415506863</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7241774594615077</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.7308956948161583</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.6985322660863538</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>479.1104999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>73.0575</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.55173926187427</v>
       </c>
       <c r="C23" t="n">
+        <v>2.056292711465103</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.386969433883211</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.056292711465103</v>
       </c>
       <c r="E23" t="n">
         <v>1.55173926187427</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01779081667306865</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.485677233488238</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2452984219057955</v>
+      </c>
       <c r="I23" t="n">
-        <v>21.69668153695258</v>
+        <v>0.2455691563008591</v>
       </c>
       <c r="J23" t="n">
-        <v>18.83524657979452</v>
+        <v>0.2427143653719218</v>
       </c>
       <c r="K23" t="n">
-        <v>14.74598713002987</v>
+        <v>0.2419351805317849</v>
       </c>
       <c r="L23" t="n">
-        <v>17.88604730943434</v>
+        <v>0.2663451460832453</v>
       </c>
       <c r="M23" t="n">
-        <v>14.60618835204604</v>
+        <v>0.2936857432519898</v>
       </c>
       <c r="N23" t="n">
-        <v>16.43537738142619</v>
+        <v>0.227537735447621</v>
       </c>
       <c r="O23" t="n">
-        <v>14.27841648884929</v>
+        <v>0.2330913532230838</v>
       </c>
       <c r="P23" t="n">
-        <v>13.04215846266289</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>11.34612234265317</v>
-      </c>
+        <v>0.2203890101376965</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>11.08575180082724</v>
+        <v>21.69578748222069</v>
       </c>
       <c r="S23" t="n">
-        <v>10.0761634108595</v>
+        <v>18.83479352435972</v>
       </c>
       <c r="T23" t="n">
-        <v>9.712970086750554</v>
+        <v>14.74632667016291</v>
       </c>
       <c r="U23" t="n">
-        <v>9.199798351945383</v>
+        <v>17.88711723265482</v>
       </c>
       <c r="V23" t="n">
-        <v>8.671351132937273</v>
+        <v>14.60588630439255</v>
       </c>
       <c r="W23" t="n">
-        <v>8.024837227756043</v>
+        <v>16.43499670952523</v>
       </c>
       <c r="X23" t="n">
-        <v>7.406450969621106</v>
+        <v>14.27832272141383</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.091398229353279</v>
+        <v>13.04218978828648</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.533176754429375</v>
+        <v>11.3458261627697</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>11.08435164165182</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>10.07665894661101</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.713398017822167</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>9.199739641624882</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>8.671018212534515</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>8.024174723920213</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>7.405274365008539</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>7.091126757026025</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.533111382772936</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15.48919912305618</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>14.27954370493162</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>13.40693486779667</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.49042742606237</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>14.27994157256218</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>13.40585767491211</v>
+      </c>
+      <c r="AV23" t="n">
         <v>12.5216064212393</v>
       </c>
-      <c r="AN23" t="n">
-        <v>12.02509227815926</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>11.44729956922142</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.33155613243226</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.60072857639102</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>9.267652161089524</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>17.34887701754356</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>17.17479629127061</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>16.24348044242841</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.06479866436919</v>
-      </c>
       <c r="AW23" t="n">
-        <v>13.64433674561772</v>
+        <v>12.02547270107128</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.81004365815078</v>
+        <v>11.44638904219418</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.19815624348402</v>
+        <v>10.33006399328016</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.162708056785972</v>
+        <v>9.600898683264797</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.122209421448446</v>
+        <v>9.26782016044311</v>
       </c>
       <c r="BB23" t="n">
+        <v>17.3482567833501</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>17.17358730878996</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>16.24429515245275</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>15.06538734282905</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>13.64475823781503</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>11.80906844893275</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>10.19821651074344</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>9.162411484457914</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.121684084500027</v>
+      </c>
+      <c r="BK23" t="n">
         <v>15.88204878736401</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>15.88204878736401</v>
       </c>
-      <c r="BD23" t="n">
-        <v>15.8694509572389</v>
-      </c>
-      <c r="BE23" t="n">
+      <c r="BM23" t="n">
+        <v>15.86945095723889</v>
+      </c>
+      <c r="BN23" t="n">
         <v>15.66390419840603</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>15.11395312111853</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>15.11395312111853</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>15.11395312111853</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>15.11395312111853</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>15.11395312111853</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>13.37161172035742</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2965198672284539</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2452802004212601</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2527213482393644</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.128600742513595</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.229445680611581</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2152477332408455</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2441511451981183</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1714277119641775</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1714273589347489</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>7.091126757026025</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>7.533111382772936</v>
       </c>
     </row>
   </sheetData>
